--- a/BaitGenes_RNA_CoExprAnalysis.xlsx
+++ b/BaitGenes_RNA_CoExprAnalysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Cannabis_Raphael\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EED449BF-FAEF-4434-866E-1CADECE162CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D38059C-F8BB-42FF-94F3-DD46F23636C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{574D1AB3-5974-479E-9C59-3C447D909BF6}"/>
   </bookViews>
@@ -273,9 +273,6 @@
     <t>B</t>
   </si>
   <si>
-    <t>AIHH</t>
-  </si>
-  <si>
     <t>ADC</t>
   </si>
   <si>
@@ -361,6 +358,9 @@
   </si>
   <si>
     <t>TYDC1</t>
+  </si>
+  <si>
+    <t>AIH</t>
   </si>
 </sst>
 </file>
@@ -861,7 +861,7 @@
         <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D5">
         <v>18</v>
@@ -878,7 +878,7 @@
         <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="D6">
         <v>9</v>
@@ -895,7 +895,7 @@
         <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D7">
         <v>8</v>
@@ -912,7 +912,7 @@
         <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D8">
         <v>6</v>
@@ -929,7 +929,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D9">
         <v>6</v>
@@ -946,7 +946,7 @@
         <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D10">
         <v>6</v>
@@ -963,7 +963,7 @@
         <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D11">
         <v>6</v>
@@ -980,7 +980,7 @@
         <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D12">
         <v>6</v>
@@ -997,7 +997,7 @@
         <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D13">
         <v>17</v>
@@ -1014,7 +1014,7 @@
         <v>63</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D14">
         <v>17</v>
@@ -1031,7 +1031,7 @@
         <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D15">
         <v>17</v>
@@ -1048,7 +1048,7 @@
         <v>64</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D16">
         <v>16</v>
@@ -1065,7 +1065,7 @@
         <v>48</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D17">
         <v>15</v>
@@ -1082,7 +1082,7 @@
         <v>65</v>
       </c>
       <c r="C18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D18">
         <v>15</v>
@@ -1099,7 +1099,7 @@
         <v>66</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D19">
         <v>15</v>
@@ -1116,7 +1116,7 @@
         <v>49</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D20">
         <v>10</v>
@@ -1133,13 +1133,13 @@
         <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D21">
         <v>19</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="29" x14ac:dyDescent="0.35">
@@ -1150,7 +1150,7 @@
         <v>53</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D22">
         <v>2</v>
@@ -1167,7 +1167,7 @@
         <v>51</v>
       </c>
       <c r="C23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D23">
         <v>2</v>
@@ -1184,7 +1184,7 @@
         <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D24">
         <v>2</v>
@@ -1198,10 +1198,10 @@
         <v>9</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D25">
         <v>2</v>
@@ -1218,7 +1218,7 @@
         <v>52</v>
       </c>
       <c r="C26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D26">
         <v>2</v>
@@ -1235,7 +1235,7 @@
         <v>54</v>
       </c>
       <c r="C27" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D27">
         <v>11</v>
@@ -1252,7 +1252,7 @@
         <v>55</v>
       </c>
       <c r="C28" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D28">
         <v>16</v>
@@ -1269,7 +1269,7 @@
         <v>56</v>
       </c>
       <c r="C29" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D29">
         <v>5</v>
@@ -1286,7 +1286,7 @@
         <v>57</v>
       </c>
       <c r="C30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -1303,7 +1303,7 @@
         <v>58</v>
       </c>
       <c r="C31" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -1320,7 +1320,7 @@
         <v>59</v>
       </c>
       <c r="C32" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D32">
         <v>1</v>
